--- a/Data/Regression Evidence 2025/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -244,7 +244,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10700239</t>
+    <t>10700447</t>
   </si>
   <si>
     <t>Passed</t>
@@ -256,10 +256,10 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>Audie</t>
-  </si>
-  <si>
-    <t>Quigley</t>
+    <t>Jaycee</t>
+  </si>
+  <si>
+    <t>Kling</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -397,22 +397,22 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10700271</t>
+    <t>10700448</t>
   </si>
   <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>Reese</t>
-  </si>
-  <si>
-    <t>Schmidt</t>
+    <t>Genevieve</t>
+  </si>
+  <si>
+    <t>Mertz</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 81078454</t>
+    <t>Auto 1253949</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -1382,7 +1382,7 @@
         <v>104</v>
       </c>
       <c r="AT2" s="18">
-        <v>9461110922</v>
+        <v>9461110965</v>
       </c>
       <c r="AU2" s="13" t="s">
         <v>105</v>
@@ -1397,7 +1397,7 @@
         <v>107</v>
       </c>
       <c r="AY2" s="19">
-        <v>152733424</v>
+        <v>152733449</v>
       </c>
       <c r="AZ2" s="13" t="s">
         <v>105</v>
@@ -1626,7 +1626,7 @@
         <v>104</v>
       </c>
       <c r="AT3" s="18">
-        <v>9461110924</v>
+        <v>9461110966</v>
       </c>
       <c r="AU3" s="13" t="s">
         <v>105</v>
@@ -1641,7 +1641,7 @@
         <v>107</v>
       </c>
       <c r="AY3" s="19">
-        <v>152733426</v>
+        <v>152733451</v>
       </c>
       <c r="AZ3" s="13" t="s">
         <v>105</v>
